--- a/Experiments/outputs/scenario_2_np.xlsx
+++ b/Experiments/outputs/scenario_2_np.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>225.8494167986039</v>
+        <v>175.2894311500679</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0991511344909668</v>
+        <v>0.1632189750671387</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>418.3481354752672</v>
+        <v>404.4319032319374</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2422280311584473</v>
+        <v>0.5136229991912842</v>
       </c>
       <c r="J2" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="M2" t="n">
-        <v>1289.707403118715</v>
+        <v>1244.094506028287</v>
       </c>
       <c r="N2" t="n">
-        <v>1.75761604309082</v>
+        <v>1.494117736816406</v>
       </c>
       <c r="O2" t="n">
-        <v>386</v>
+        <v>418</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1037</v>
+        <v>1161</v>
       </c>
       <c r="R2" t="n">
-        <v>0.824883212849314</v>
+        <v>0.8591028010326394</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6756255454038367</v>
+        <v>0.6749186647218087</v>
       </c>
     </row>
     <row r="3">
@@ -591,55 +591,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>233.1603879982925</v>
+        <v>214.6709821148571</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06901884078979492</v>
+        <v>0.1180062294006348</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>414.1016456675206</v>
+        <v>456.2484787852729</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2017791271209717</v>
+        <v>0.4006671905517578</v>
       </c>
       <c r="J3" t="n">
         <v>88</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M3" t="n">
-        <v>1314.15190410687</v>
+        <v>1299.912692223731</v>
       </c>
       <c r="N3" t="n">
-        <v>1.566690921783447</v>
+        <v>1.655410051345825</v>
       </c>
       <c r="O3" t="n">
-        <v>381</v>
+        <v>416</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>975</v>
+        <v>1127</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8225772931807652</v>
+        <v>0.8348573843466176</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6848905789555932</v>
+        <v>0.6490160596826091</v>
       </c>
     </row>
     <row r="4">
@@ -652,55 +652,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>229.0056657271801</v>
+        <v>210.9161276401733</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06118607521057129</v>
+        <v>0.1229879856109619</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>458.1057520827114</v>
+        <v>484.6695396358235</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1870882511138916</v>
+        <v>0.4896767139434814</v>
       </c>
       <c r="J4" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K4" t="n">
         <v>13</v>
       </c>
       <c r="L4" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="M4" t="n">
-        <v>1346.98325363133</v>
+        <v>1344.691761150218</v>
       </c>
       <c r="N4" t="n">
-        <v>1.391891002655029</v>
+        <v>2.512400150299072</v>
       </c>
       <c r="O4" t="n">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1065</v>
+        <v>1172</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8299862562434953</v>
+        <v>0.843149089082125</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6599024146382632</v>
+        <v>0.6395682983725219</v>
       </c>
     </row>
     <row r="5">
@@ -713,55 +713,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>199.7114713289461</v>
+        <v>224.0262029519204</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0569767951965332</v>
+        <v>0.1351919174194336</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>430.3513897011321</v>
+        <v>446.6095177741007</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1601521968841553</v>
+        <v>0.5571951866149902</v>
       </c>
       <c r="J5" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K5" t="n">
         <v>14</v>
       </c>
       <c r="L5" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="M5" t="n">
-        <v>1318.773089933966</v>
+        <v>1284.465865002547</v>
       </c>
       <c r="N5" t="n">
-        <v>1.333333015441895</v>
+        <v>1.859326839447021</v>
       </c>
       <c r="O5" t="n">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1056</v>
+        <v>1135</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8485626732503724</v>
+        <v>0.825588044761722</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6736729062899814</v>
+        <v>0.6522994266000094</v>
       </c>
     </row>
     <row r="6">
@@ -774,55 +774,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>195.3384278253793</v>
+        <v>189.8507163642176</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05133700370788574</v>
+        <v>0.1017899513244629</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>424.1585864375375</v>
+        <v>395.4154823404788</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1604220867156982</v>
+        <v>0.5867011547088623</v>
       </c>
       <c r="J6" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M6" t="n">
-        <v>1282.14465514534</v>
+        <v>1265.037271408971</v>
       </c>
       <c r="N6" t="n">
-        <v>1.484525203704834</v>
+        <v>1.752810955047607</v>
       </c>
       <c r="O6" t="n">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1041</v>
+        <v>1090</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8476471223106753</v>
+        <v>0.8499248040709774</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6691803965056843</v>
+        <v>0.6874278005263247</v>
       </c>
     </row>
     <row r="7">
@@ -835,55 +835,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>220.4060321574352</v>
+        <v>241.4842595773175</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0642540454864502</v>
+        <v>0.1031150817871094</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>450.2263141932423</v>
+        <v>389.5240791285672</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1972401142120361</v>
+        <v>0.3128771781921387</v>
       </c>
       <c r="J7" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="M7" t="n">
-        <v>1304.688742439834</v>
+        <v>1327.577903809781</v>
       </c>
       <c r="N7" t="n">
-        <v>1.554963827133179</v>
+        <v>1.462972164154053</v>
       </c>
       <c r="O7" t="n">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1082</v>
+        <v>1138</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8310661961064638</v>
+        <v>0.8181016278710842</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6549166866027399</v>
+        <v>0.706590417021298</v>
       </c>
     </row>
     <row r="8">
@@ -896,55 +896,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>183.7638927756452</v>
+        <v>222.7288885992924</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04523587226867676</v>
+        <v>0.1068217754364014</v>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H8" t="n">
+        <v>439.2204451279007</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.4089667797088623</v>
+      </c>
+      <c r="J8" t="n">
+        <v>84</v>
+      </c>
+      <c r="K8" t="n">
+        <v>15</v>
+      </c>
+      <c r="L8" t="n">
+        <v>107</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1333.738203179604</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.38732385635376</v>
+      </c>
+      <c r="O8" t="n">
+        <v>403</v>
+      </c>
+      <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>414.5073853359628</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.1513440608978271</v>
-      </c>
-      <c r="J8" t="n">
-        <v>79</v>
-      </c>
-      <c r="K8" t="n">
-        <v>14</v>
-      </c>
-      <c r="L8" t="n">
-        <v>92</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1344.921301140033</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.578564882278442</v>
-      </c>
-      <c r="O8" t="n">
-        <v>390</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
       <c r="Q8" t="n">
-        <v>1057</v>
+        <v>1045</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8633645755927307</v>
+        <v>0.8330040422713306</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6917980368185096</v>
+        <v>0.6706846635413094</v>
       </c>
     </row>
     <row r="9">
@@ -957,55 +957,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>248.6321377095756</v>
+        <v>238.2412044157489</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05998325347900391</v>
+        <v>0.09447503089904785</v>
       </c>
       <c r="E9" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
         <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>466.0267633460075</v>
+        <v>408.0710350300653</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1696898937225342</v>
+        <v>0.2635219097137451</v>
       </c>
       <c r="J9" t="n">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="K9" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L9" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="M9" t="n">
-        <v>1327.159569556041</v>
+        <v>1313.525025412165</v>
       </c>
       <c r="N9" t="n">
-        <v>1.500862836837769</v>
+        <v>1.425438165664673</v>
       </c>
       <c r="O9" t="n">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1076</v>
+        <v>1135</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8126584448373849</v>
+        <v>0.8186245409820097</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6488540081868965</v>
+        <v>0.6893313586453987</v>
       </c>
     </row>
     <row r="10">
@@ -1018,55 +1018,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>170.6979969113293</v>
+        <v>207.3623356919682</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05691790580749512</v>
+        <v>0.09790992736816406</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>418.4156924033337</v>
+        <v>409.5461642932726</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1730291843414307</v>
+        <v>0.4370861053466797</v>
       </c>
       <c r="J10" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L10" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="M10" t="n">
-        <v>1322.467918408934</v>
+        <v>1248.500767178122</v>
       </c>
       <c r="N10" t="n">
-        <v>1.397066831588745</v>
+        <v>1.512146949768066</v>
       </c>
       <c r="O10" t="n">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1122</v>
+        <v>1090</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8709246594679615</v>
+        <v>0.8339109264941412</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6836099488093964</v>
+        <v>0.6719696334517005</v>
       </c>
     </row>
     <row r="11">
@@ -1079,55 +1079,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>197.0228341101223</v>
+        <v>163.286142610806</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04725313186645508</v>
+        <v>0.08981013298034668</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>392.4219675711707</v>
+        <v>417.8211968384668</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1570301055908203</v>
+        <v>0.3440568447113037</v>
       </c>
       <c r="J11" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M11" t="n">
-        <v>1296.279225946918</v>
+        <v>1317.176890123485</v>
       </c>
       <c r="N11" t="n">
-        <v>1.201623201370239</v>
+        <v>1.409952163696289</v>
       </c>
       <c r="O11" t="n">
-        <v>389</v>
+        <v>424</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1048</v>
+        <v>1137</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8480089550411493</v>
+        <v>0.8760332466845072</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6972704956491834</v>
+        <v>0.6827903678151414</v>
       </c>
     </row>
     <row r="12">
@@ -1140,55 +1140,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>184.9275375892646</v>
+        <v>236.1267718748856</v>
       </c>
       <c r="D12" t="n">
-        <v>0.09294795989990234</v>
+        <v>0.1020269393920898</v>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G12" t="n">
         <v>9</v>
       </c>
-      <c r="G12" t="n">
-        <v>6</v>
-      </c>
       <c r="H12" t="n">
-        <v>436.1070759579749</v>
+        <v>442.8211517422941</v>
       </c>
       <c r="I12" t="n">
-        <v>0.253061056137085</v>
+        <v>0.4251546859741211</v>
       </c>
       <c r="J12" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L12" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M12" t="n">
-        <v>1313.124376892496</v>
+        <v>1302.075926413506</v>
       </c>
       <c r="N12" t="n">
-        <v>2.683348894119263</v>
+        <v>1.48112678527832</v>
       </c>
       <c r="O12" t="n">
-        <v>380</v>
+        <v>425</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1036</v>
+        <v>1129</v>
       </c>
       <c r="R12" t="n">
-        <v>0.859169823633238</v>
+        <v>0.8186536076085184</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6678859340118102</v>
+        <v>0.659911420863129</v>
       </c>
     </row>
     <row r="13">
@@ -1201,55 +1201,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>222.2545482775515</v>
+        <v>226.1298180083519</v>
       </c>
       <c r="D13" t="n">
-        <v>0.09359407424926758</v>
+        <v>0.107806921005249</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
       </c>
       <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>511.8201725029398</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7657980918884277</v>
+      </c>
+      <c r="J13" t="n">
+        <v>112</v>
+      </c>
+      <c r="K13" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" t="n">
+        <v>141</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1305.191920270914</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.46014404296875</v>
+      </c>
+      <c r="O13" t="n">
+        <v>404</v>
+      </c>
+      <c r="P13" t="n">
         <v>3</v>
       </c>
-      <c r="H13" t="n">
-        <v>409.0420672371199</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.4539179801940918</v>
-      </c>
-      <c r="J13" t="n">
-        <v>93</v>
-      </c>
-      <c r="K13" t="n">
-        <v>9</v>
-      </c>
-      <c r="L13" t="n">
-        <v>100</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1307.471805648713</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.963839054107666</v>
-      </c>
-      <c r="O13" t="n">
-        <v>374</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
       <c r="Q13" t="n">
-        <v>1012</v>
+        <v>1068</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8300119763062286</v>
+        <v>0.8267459256402577</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6871503725970058</v>
+        <v>0.6078583045497991</v>
       </c>
     </row>
     <row r="14">
@@ -1262,55 +1262,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>214.6827806031866</v>
+        <v>225.1185871302368</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1313138008117676</v>
+        <v>0.1278829574584961</v>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>390.226252564886</v>
+        <v>352.7127919080881</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2634899616241455</v>
+        <v>0.273463249206543</v>
       </c>
       <c r="J14" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="K14" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L14" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="M14" t="n">
-        <v>1389.021805764062</v>
+        <v>1283.241301468704</v>
       </c>
       <c r="N14" t="n">
-        <v>1.573587894439697</v>
+        <v>1.45433497428894</v>
       </c>
       <c r="O14" t="n">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1118</v>
+        <v>1155</v>
       </c>
       <c r="R14" t="n">
-        <v>0.845443189075714</v>
+        <v>0.8245703385071984</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7190639837722106</v>
+        <v>0.7251391523134433</v>
       </c>
     </row>
     <row r="15">
@@ -1323,55 +1323,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>233.884453560597</v>
+        <v>208.9199612166701</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07420206069946289</v>
+        <v>0.09869098663330078</v>
       </c>
       <c r="E15" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>506.2563280977224</v>
+        <v>433.5954456585281</v>
       </c>
       <c r="I15" t="n">
-        <v>0.536963939666748</v>
+        <v>0.3894097805023193</v>
       </c>
       <c r="J15" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="K15" t="n">
         <v>15</v>
       </c>
       <c r="L15" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M15" t="n">
-        <v>1311.332401325452</v>
+        <v>1280.727347578614</v>
       </c>
       <c r="N15" t="n">
-        <v>1.823900938034058</v>
+        <v>1.421369791030884</v>
       </c>
       <c r="O15" t="n">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>1098</v>
+        <v>1152</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8216436554727129</v>
+        <v>0.8368739750801284</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6139374520251195</v>
+        <v>0.6614459381395282</v>
       </c>
     </row>
     <row r="16">
@@ -1384,55 +1384,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>198.6733694517909</v>
+        <v>198.2720459313445</v>
       </c>
       <c r="D16" t="n">
-        <v>0.09557080268859863</v>
+        <v>0.1008880138397217</v>
       </c>
       <c r="E16" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>455.4062898399191</v>
+        <v>427.4458227442288</v>
       </c>
       <c r="I16" t="n">
-        <v>0.256864070892334</v>
+        <v>0.3275372982025146</v>
       </c>
       <c r="J16" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="K16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L16" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="M16" t="n">
-        <v>1286.634747273593</v>
+        <v>1309.582000525103</v>
       </c>
       <c r="N16" t="n">
-        <v>1.506080150604248</v>
+        <v>1.413429975509644</v>
       </c>
       <c r="O16" t="n">
-        <v>391</v>
+        <v>436</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1068</v>
+        <v>1202</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8455868148495258</v>
+        <v>0.8485989836055753</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6460485069248014</v>
+        <v>0.6736013303688994</v>
       </c>
     </row>
     <row r="17">
@@ -1445,55 +1445,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>216.8090258834588</v>
+        <v>241.6724230417476</v>
       </c>
       <c r="D17" t="n">
-        <v>0.06092691421508789</v>
+        <v>0.09149909019470215</v>
       </c>
       <c r="E17" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>453.7887266445742</v>
+        <v>498.5691899538097</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1752111911773682</v>
+        <v>0.4838488101959229</v>
       </c>
       <c r="J17" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L17" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="M17" t="n">
-        <v>1352.337368143314</v>
+        <v>1294.558910732789</v>
       </c>
       <c r="N17" t="n">
-        <v>1.308697700500488</v>
+        <v>1.412454128265381</v>
       </c>
       <c r="O17" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8396782999636209</v>
+        <v>0.8133167822351567</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6644411835874938</v>
+        <v>0.614873308722897</v>
       </c>
     </row>
     <row r="18">
@@ -1506,55 +1506,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>217.496281582598</v>
+        <v>213.3355730165729</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05812788009643555</v>
+        <v>0.09928989410400391</v>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>438.5691216340733</v>
+        <v>414.6467257612132</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1928009986877441</v>
+        <v>0.4390027523040771</v>
       </c>
       <c r="J18" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K18" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="M18" t="n">
-        <v>1335.673586940246</v>
+        <v>1247.886732604567</v>
       </c>
       <c r="N18" t="n">
-        <v>1.610076189041138</v>
+        <v>1.538657903671265</v>
       </c>
       <c r="O18" t="n">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8371635976714661</v>
+        <v>0.8290425184893964</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6716494763973397</v>
+        <v>0.6677208636590197</v>
       </c>
     </row>
     <row r="19">
@@ -1567,55 +1567,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>249.648240760448</v>
+        <v>218.7368037114181</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06546783447265625</v>
+        <v>0.08836770057678223</v>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>482.2029424712906</v>
+        <v>409.3704444844087</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2162530422210693</v>
+        <v>0.3465609550476074</v>
       </c>
       <c r="J19" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K19" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L19" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="M19" t="n">
-        <v>1232.00790331898</v>
+        <v>1344.912776627013</v>
       </c>
       <c r="N19" t="n">
-        <v>1.427268028259277</v>
+        <v>1.351323843002319</v>
       </c>
       <c r="O19" t="n">
-        <v>390</v>
+        <v>424</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1077</v>
+        <v>1169</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7973647408527934</v>
+        <v>0.8373598589344944</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6086040185519467</v>
+        <v>0.6956156179056509</v>
       </c>
     </row>
     <row r="20">
@@ -1628,55 +1628,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>219.1666036828231</v>
+        <v>200.0322904658236</v>
       </c>
       <c r="D20" t="n">
-        <v>0.06067085266113281</v>
+        <v>0.1155052185058594</v>
       </c>
       <c r="E20" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>407.5615008111008</v>
+        <v>459.6514312750754</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2070670127868652</v>
+        <v>0.4969220161437988</v>
       </c>
       <c r="J20" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="K20" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L20" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M20" t="n">
-        <v>1302.669711749831</v>
+        <v>1319.712625435347</v>
       </c>
       <c r="N20" t="n">
-        <v>1.561733961105347</v>
+        <v>1.364922046661377</v>
       </c>
       <c r="O20" t="n">
-        <v>374</v>
+        <v>422</v>
       </c>
       <c r="P20" t="n">
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>990</v>
+        <v>1129</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8317558152262371</v>
+        <v>0.8484273874398702</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6871336631726568</v>
+        <v>0.6517033917717916</v>
       </c>
     </row>
     <row r="21">
@@ -1689,55 +1689,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>236.3986413592714</v>
+        <v>209.6775745750859</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0659019947052002</v>
+        <v>0.0958249568939209</v>
       </c>
       <c r="E21" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>497.7857925807019</v>
+        <v>488.166920264996</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2128040790557861</v>
+        <v>0.507746696472168</v>
       </c>
       <c r="J21" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K21" t="n">
         <v>13</v>
       </c>
       <c r="L21" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="M21" t="n">
-        <v>1339.186323365373</v>
+        <v>1329.46787215353</v>
       </c>
       <c r="N21" t="n">
-        <v>1.392359256744385</v>
+        <v>1.360553979873657</v>
       </c>
       <c r="O21" t="n">
-        <v>377</v>
+        <v>424</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1029</v>
+        <v>1127</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8234759142662077</v>
+        <v>0.8422845869637745</v>
       </c>
       <c r="S21" t="n">
-        <v>0.62829235641403</v>
+        <v>0.6328102916287538</v>
       </c>
     </row>
     <row r="22">
@@ -1750,55 +1750,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>226.8210578800787</v>
+        <v>200.7974924505939</v>
       </c>
       <c r="D22" t="n">
-        <v>0.05085492134094238</v>
+        <v>0.1020088195800781</v>
       </c>
       <c r="E22" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F22" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>381.4135539416546</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.4886150360107422</v>
+      </c>
+      <c r="J22" t="n">
+        <v>84</v>
+      </c>
+      <c r="K22" t="n">
         <v>11</v>
       </c>
-      <c r="G22" t="n">
-        <v>7</v>
-      </c>
-      <c r="H22" t="n">
-        <v>453.1450887577472</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.1796588897705078</v>
-      </c>
-      <c r="J22" t="n">
-        <v>101</v>
-      </c>
-      <c r="K22" t="n">
-        <v>12</v>
-      </c>
       <c r="L22" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="M22" t="n">
-        <v>1322.155180349856</v>
+        <v>1358.683806023245</v>
       </c>
       <c r="N22" t="n">
-        <v>1.375871896743774</v>
+        <v>1.736467838287354</v>
       </c>
       <c r="O22" t="n">
-        <v>392</v>
+        <v>429</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1083</v>
+        <v>1132</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8284459636424376</v>
+        <v>0.8522117570251231</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6572678491205245</v>
+        <v>0.7192771767420851</v>
       </c>
     </row>
     <row r="23">
@@ -1811,55 +1811,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>267.8772861339522</v>
+        <v>240.6246190040194</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0611121654510498</v>
+        <v>0.09408903121948242</v>
       </c>
       <c r="E23" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>486.9935166656628</v>
+        <v>386.5909333522573</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1979372501373291</v>
+        <v>0.4265470504760742</v>
       </c>
       <c r="J23" t="n">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="K23" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L23" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="M23" t="n">
-        <v>1369.117794869887</v>
+        <v>1338.014150607058</v>
       </c>
       <c r="N23" t="n">
-        <v>1.434969186782837</v>
+        <v>1.677558898925781</v>
       </c>
       <c r="O23" t="n">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1006</v>
+        <v>1138</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8043431418847276</v>
+        <v>0.8201628742903444</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6443012292364925</v>
+        <v>0.7110711174639963</v>
       </c>
     </row>
     <row r="24">
@@ -1872,55 +1872,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>225.4012105603981</v>
+        <v>206.2963148070109</v>
       </c>
       <c r="D24" t="n">
-        <v>0.05439901351928711</v>
+        <v>0.1529479026794434</v>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
         <v>10</v>
       </c>
       <c r="H24" t="n">
-        <v>465.1008937587467</v>
+        <v>423.6181003328397</v>
       </c>
       <c r="I24" t="n">
-        <v>0.175246000289917</v>
+        <v>0.5032157897949219</v>
       </c>
       <c r="J24" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="K24" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L24" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M24" t="n">
-        <v>1327.336677992436</v>
+        <v>1259.970904334942</v>
       </c>
       <c r="N24" t="n">
-        <v>1.730728387832642</v>
+        <v>1.364723205566406</v>
       </c>
       <c r="O24" t="n">
-        <v>374</v>
+        <v>412</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>941</v>
+        <v>1134</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8301853521434276</v>
+        <v>0.8362689851827162</v>
       </c>
       <c r="S24" t="n">
-        <v>0.649598401467968</v>
+        <v>0.6637873947125466</v>
       </c>
     </row>
     <row r="25">
@@ -1933,55 +1933,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>235.0042361303005</v>
+        <v>226.8408609136515</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08007502555847168</v>
+        <v>0.0984809398651123</v>
       </c>
       <c r="E25" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H25" t="n">
-        <v>507.147958775751</v>
+        <v>463.0020281889359</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2289719581604004</v>
+        <v>0.3829629421234131</v>
       </c>
       <c r="J25" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K25" t="n">
         <v>14</v>
       </c>
       <c r="L25" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="M25" t="n">
-        <v>1306.608179849658</v>
+        <v>1328.214527654436</v>
       </c>
       <c r="N25" t="n">
-        <v>1.522444009780884</v>
+        <v>1.357640981674194</v>
       </c>
       <c r="O25" t="n">
-        <v>391</v>
+        <v>429</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1051</v>
+        <v>1172</v>
       </c>
       <c r="R25" t="n">
-        <v>0.820141768776206</v>
+        <v>0.8292136878564024</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6118591888548371</v>
+        <v>0.6514102062965871</v>
       </c>
     </row>
     <row r="26">
@@ -1994,55 +1994,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>174.3426319456358</v>
+        <v>224.1123281067658</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08913207054138184</v>
+        <v>0.09434199333190918</v>
       </c>
       <c r="E26" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>414.5766982558604</v>
+        <v>433.3692868565548</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2469792366027832</v>
+        <v>0.4333250522613525</v>
       </c>
       <c r="J26" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K26" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L26" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="M26" t="n">
-        <v>1317.474997077488</v>
+        <v>1303.713715087069</v>
       </c>
       <c r="N26" t="n">
-        <v>1.359154224395752</v>
+        <v>1.571722030639648</v>
       </c>
       <c r="O26" t="n">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1084</v>
+        <v>1162</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8676691152907081</v>
+        <v>0.8280969774934075</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6853248075481491</v>
+        <v>0.6675886110259934</v>
       </c>
     </row>
     <row r="27">
@@ -2055,55 +2055,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>254.9480567908708</v>
+        <v>238.8485668366702</v>
       </c>
       <c r="D27" t="n">
-        <v>0.04977512359619141</v>
+        <v>0.09551095962524414</v>
       </c>
       <c r="E27" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>511.5370710808579</v>
+        <v>463.0868258474729</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2200841903686523</v>
+        <v>0.3368411064147949</v>
       </c>
       <c r="J27" t="n">
+        <v>73</v>
+      </c>
+      <c r="K27" t="n">
+        <v>18</v>
+      </c>
+      <c r="L27" t="n">
         <v>104</v>
       </c>
-      <c r="K27" t="n">
-        <v>14</v>
-      </c>
-      <c r="L27" t="n">
-        <v>116</v>
-      </c>
       <c r="M27" t="n">
-        <v>1271.432987433155</v>
+        <v>1264.036323895007</v>
       </c>
       <c r="N27" t="n">
-        <v>1.422191143035889</v>
+        <v>1.376940965652466</v>
       </c>
       <c r="O27" t="n">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="R27" t="n">
-        <v>0.7994797529159794</v>
+        <v>0.8110429563442598</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5976688695850344</v>
+        <v>0.633644368367109</v>
       </c>
     </row>
     <row r="28">
@@ -2116,55 +2116,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>209.838368064226</v>
+        <v>246.5199397088385</v>
       </c>
       <c r="D28" t="n">
-        <v>0.06002402305603027</v>
+        <v>0.106421947479248</v>
       </c>
       <c r="E28" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>455.7351715134324</v>
+        <v>480.8399060055178</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1785891056060791</v>
+        <v>0.5051932334899902</v>
       </c>
       <c r="J28" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K28" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L28" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="M28" t="n">
-        <v>1346.500460715103</v>
+        <v>1305.694088111282</v>
       </c>
       <c r="N28" t="n">
-        <v>1.582253932952881</v>
+        <v>1.388653039932251</v>
       </c>
       <c r="O28" t="n">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1011</v>
+        <v>1063</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8441601958659677</v>
+        <v>0.8111962503671627</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6615410207350398</v>
+        <v>0.6317361697631148</v>
       </c>
     </row>
     <row r="29">
@@ -2177,55 +2177,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>220.3213872250064</v>
+        <v>218.0619302048421</v>
       </c>
       <c r="D29" t="n">
-        <v>0.06796622276306152</v>
+        <v>0.1102828979492188</v>
       </c>
       <c r="E29" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>460.590166512435</v>
+        <v>436.1346111019524</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1855459213256836</v>
+        <v>0.4740028381347656</v>
       </c>
       <c r="J29" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L29" t="n">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="M29" t="n">
-        <v>1305.410219251962</v>
+        <v>1300.550947529897</v>
       </c>
       <c r="N29" t="n">
-        <v>1.750005006790161</v>
+        <v>1.404371738433838</v>
       </c>
       <c r="O29" t="n">
-        <v>374</v>
+        <v>415</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1016</v>
+        <v>1129</v>
       </c>
       <c r="R29" t="n">
-        <v>0.831224404424184</v>
+        <v>0.8323311127341827</v>
       </c>
       <c r="S29" t="n">
-        <v>0.6471682543006546</v>
+        <v>0.6646539592083711</v>
       </c>
     </row>
     <row r="30">
@@ -2238,55 +2238,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>213.9072464915504</v>
+        <v>253.8110175023794</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05449581146240234</v>
+        <v>0.1053121089935303</v>
       </c>
       <c r="E30" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F30" t="n">
+        <v>13</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>462.7967456890209</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4969189167022705</v>
+      </c>
+      <c r="J30" t="n">
+        <v>99</v>
+      </c>
+      <c r="K30" t="n">
         <v>11</v>
       </c>
-      <c r="G30" t="n">
-        <v>6</v>
-      </c>
-      <c r="H30" t="n">
-        <v>473.292088281558</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.1748521327972412</v>
-      </c>
-      <c r="J30" t="n">
-        <v>89</v>
-      </c>
-      <c r="K30" t="n">
-        <v>14</v>
-      </c>
       <c r="L30" t="n">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="M30" t="n">
-        <v>1326.050577377307</v>
+        <v>1371.495036330508</v>
       </c>
       <c r="N30" t="n">
-        <v>1.62483811378479</v>
+        <v>1.540808916091919</v>
       </c>
       <c r="O30" t="n">
-        <v>389</v>
+        <v>426</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1075</v>
+        <v>1111</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8386884707560543</v>
+        <v>0.8149384352265238</v>
       </c>
       <c r="S30" t="n">
-        <v>0.6430814206064103</v>
+        <v>0.6625603932718176</v>
       </c>
     </row>
     <row r="31">
@@ -2299,25 +2299,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>210.8128690501005</v>
+        <v>221.6321537680605</v>
       </c>
       <c r="D31" t="n">
-        <v>0.05728793144226074</v>
+        <v>0.09264707565307617</v>
       </c>
       <c r="E31" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H31" t="n">
-        <v>488.7635792408006</v>
+        <v>442.9600351737373</v>
       </c>
       <c r="I31" t="n">
-        <v>0.182854175567627</v>
+        <v>0.4274940490722656</v>
       </c>
       <c r="J31" t="n">
         <v>94</v>
@@ -2326,28 +2326,28 @@
         <v>14</v>
       </c>
       <c r="L31" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="M31" t="n">
-        <v>1358.230002589602</v>
+        <v>1329.960614244722</v>
       </c>
       <c r="N31" t="n">
-        <v>1.489304065704346</v>
+        <v>1.456704139709473</v>
       </c>
       <c r="O31" t="n">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1049</v>
+        <v>1125</v>
       </c>
       <c r="R31" t="n">
-        <v>0.8447885346015295</v>
+        <v>0.8333543479451651</v>
       </c>
       <c r="S31" t="n">
-        <v>0.6401466774339222</v>
+        <v>0.6669374788776793</v>
       </c>
     </row>
   </sheetData>
